--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_computer_services.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_computer_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tpex_8455" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,121 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08019999999999999</v>
+        <v>-0.0308</v>
       </c>
       <c r="E2">
-        <v>-0.232</v>
+        <v>-0.122</v>
       </c>
       <c r="G2">
-        <v>-0.003785557986870897</v>
+        <v>0.01428879310344828</v>
       </c>
       <c r="H2">
-        <v>-0.005098468271334792</v>
+        <v>0.01366379310344828</v>
       </c>
       <c r="I2">
-        <v>-0.01584245076586433</v>
+        <v>0.006681034482758621</v>
       </c>
       <c r="J2">
-        <v>-0.007921225382932166</v>
+        <v>0.003340517241379311</v>
       </c>
       <c r="K2">
-        <v>0.435</v>
+        <v>0.784</v>
       </c>
       <c r="L2">
-        <v>0.009518599562363238</v>
+        <v>0.01689655172413793</v>
       </c>
       <c r="M2">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.006606334841628959</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.3356321839080459</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.006606334841628959</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.3356321839080459</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>13.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="V2">
-        <v>0.6289592760180995</v>
+        <v>0.5114754098360655</v>
       </c>
       <c r="W2">
-        <v>0.02265625</v>
+        <v>0.03939698492462312</v>
       </c>
       <c r="X2">
-        <v>0.1130564464735889</v>
+        <v>0.1741940407399773</v>
       </c>
       <c r="Y2">
-        <v>-0.09040019647358891</v>
+        <v>-0.1347970558153542</v>
       </c>
       <c r="Z2">
-        <v>1.575862068965517</v>
+        <v>1.705882352941177</v>
       </c>
       <c r="AA2">
-        <v>-0.01248275862068965</v>
+        <v>0.005698529411764706</v>
       </c>
       <c r="AB2">
-        <v>0.07165166029299506</v>
+        <v>0.1220145112108575</v>
       </c>
       <c r="AC2">
-        <v>-0.08413441891368471</v>
+        <v>-0.1163159817990927</v>
       </c>
       <c r="AD2">
-        <v>21.2</v>
+        <v>16</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>21.2</v>
+        <v>16</v>
       </c>
       <c r="AG2">
-        <v>7.299999999999999</v>
+        <v>6.640000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.489607390300231</v>
+        <v>0.4664723032069971</v>
       </c>
       <c r="AI2">
-        <v>0.4598698481561823</v>
+        <v>0.4371584699453552</v>
       </c>
       <c r="AJ2">
-        <v>0.2482993197278911</v>
+        <v>0.2662389735364876</v>
       </c>
       <c r="AK2">
-        <v>0.2267080745341615</v>
+        <v>0.2437591776798825</v>
       </c>
       <c r="AL2">
-        <v>0.313</v>
+        <v>0.267</v>
       </c>
       <c r="AM2">
-        <v>0.213</v>
+        <v>0.153</v>
       </c>
       <c r="AN2">
-        <v>-235.5555555555555</v>
+        <v>22.56699576868829</v>
       </c>
       <c r="AO2">
-        <v>-2.313099041533546</v>
+        <v>1.161048689138577</v>
       </c>
       <c r="AP2">
-        <v>-81.1111111111111</v>
+        <v>9.365303244005643</v>
       </c>
       <c r="AQ2">
-        <v>-3.39906103286385</v>
+        <v>2.026143790849673</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +721,8830 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.08019999999999999</v>
+        <v>-0.0308</v>
       </c>
       <c r="E3">
-        <v>-0.232</v>
+        <v>-0.122</v>
       </c>
       <c r="G3">
-        <v>-0.003785557986870897</v>
+        <v>0.01428879310344828</v>
       </c>
       <c r="H3">
-        <v>-0.005098468271334792</v>
+        <v>0.01366379310344828</v>
       </c>
       <c r="I3">
-        <v>-0.01584245076586433</v>
+        <v>0.006681034482758621</v>
       </c>
       <c r="J3">
-        <v>-0.007921225382932166</v>
+        <v>0.003340517241379311</v>
       </c>
       <c r="K3">
-        <v>0.435</v>
+        <v>0.784</v>
       </c>
       <c r="L3">
-        <v>0.009518599562363238</v>
+        <v>0.01689655172413793</v>
       </c>
       <c r="M3">
-        <v>0.146</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.006606334841628959</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3356321839080459</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.146</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.006606334841628959</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3356321839080459</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="U3">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="V3">
+        <v>0.5114754098360655</v>
+      </c>
+      <c r="W3">
+        <v>0.03939698492462312</v>
+      </c>
+      <c r="X3">
+        <v>0.1741940407399773</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1347970558153542</v>
+      </c>
+      <c r="Z3">
+        <v>1.705882352941177</v>
+      </c>
+      <c r="AA3">
+        <v>0.005698529411764706</v>
+      </c>
+      <c r="AB3">
+        <v>0.1220145112108575</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1163159817990927</v>
+      </c>
+      <c r="AD3">
+        <v>16</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>16</v>
+      </c>
+      <c r="AG3">
+        <v>6.640000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>0.4664723032069971</v>
+      </c>
+      <c r="AI3">
+        <v>0.4371584699453552</v>
+      </c>
+      <c r="AJ3">
+        <v>0.2662389735364876</v>
+      </c>
+      <c r="AK3">
+        <v>0.2437591776798825</v>
+      </c>
+      <c r="AL3">
+        <v>0.267</v>
+      </c>
+      <c r="AM3">
+        <v>0.153</v>
+      </c>
+      <c r="AN3">
+        <v>22.56699576868829</v>
+      </c>
+      <c r="AO3">
+        <v>1.161048689138577</v>
+      </c>
+      <c r="AP3">
+        <v>9.365303244005643</v>
+      </c>
+      <c r="AQ3">
+        <v>2.026143790849673</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Daito Me Holdings Co., Ltd (TPEX:8455)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TPEX:8455</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Computer Services</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.466472303206997</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>18.3</v>
+      </c>
+      <c r="H2">
+        <v>38.0902229613707</v>
+      </c>
+      <c r="I2">
+        <v>24.94</v>
+      </c>
+      <c r="J2">
+        <v>28.7302229613707</v>
+      </c>
+      <c r="K2">
+        <v>16</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.122014511210857</v>
+      </c>
+      <c r="N2">
+        <v>0.111036470715498</v>
+      </c>
+      <c r="O2">
+        <v>0.0623341743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.174194040739977</v>
+      </c>
+      <c r="T2">
+        <v>0.111036470715498</v>
+      </c>
+      <c r="U2">
+        <v>1.94844735605056</v>
+      </c>
+      <c r="V2">
+        <v>1.03955063019607</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>18.3</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0623341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0.709</v>
+      </c>
+      <c r="AH2">
+        <v>0.399</v>
+      </c>
+      <c r="AI2">
+        <v>0.453</v>
+      </c>
+      <c r="AJ2">
+        <v>16</v>
+      </c>
+      <c r="AK2">
+        <v>16</v>
+      </c>
+      <c r="AL2">
+        <v>0.267</v>
+      </c>
+      <c r="AM2">
+        <v>16</v>
+      </c>
+      <c r="AN2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1110364707154981</v>
+      </c>
+      <c r="C2">
+        <v>38.09022296137069</v>
+      </c>
+      <c r="D2">
+        <v>28.73022296137069</v>
+      </c>
+      <c r="E2">
+        <v>-16</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H2">
+        <v>18.3</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.709</v>
+      </c>
+      <c r="K2">
+        <v>0.399</v>
+      </c>
+      <c r="L2">
+        <v>0.31</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.31</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0.31</v>
+      </c>
+      <c r="Q2">
+        <v>0.709</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1110364707154981</v>
+      </c>
+      <c r="T2">
+        <v>1.039550630196071</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1111054707154981</v>
+      </c>
+      <c r="C3">
+        <v>37.71980615093133</v>
+      </c>
+      <c r="D3">
+        <v>28.70280615093134</v>
+      </c>
+      <c r="E3">
+        <v>-15.657</v>
+      </c>
+      <c r="F3">
+        <v>0.343</v>
+      </c>
+      <c r="G3">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H3">
+        <v>18.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0.709</v>
+      </c>
+      <c r="K3">
+        <v>0.399</v>
+      </c>
+      <c r="L3">
+        <v>0.31</v>
+      </c>
+      <c r="M3">
+        <v>0.0156751</v>
+      </c>
+      <c r="N3">
+        <v>0.2943249</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0.2943249</v>
+      </c>
+      <c r="Q3">
+        <v>0.6933248999999999</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1117661320358567</v>
+      </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.050051141612193</v>
       </c>
       <c r="U3">
-        <v>13.9</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.6289592760180995</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.02265625</v>
-      </c>
-      <c r="X3">
-        <v>0.1130564464735889</v>
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.09040019647358891</v>
+        <v>19.77658834712378</v>
       </c>
       <c r="Z3">
-        <v>1.575862068965517</v>
-      </c>
-      <c r="AA3">
-        <v>-0.01248275862068965</v>
-      </c>
-      <c r="AB3">
-        <v>0.07165166029299506</v>
-      </c>
-      <c r="AC3">
-        <v>-0.08413441891368471</v>
-      </c>
-      <c r="AD3">
-        <v>21.2</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>21.2</v>
-      </c>
-      <c r="AG3">
-        <v>7.299999999999999</v>
-      </c>
-      <c r="AH3">
-        <v>0.489607390300231</v>
-      </c>
-      <c r="AI3">
-        <v>0.4598698481561823</v>
-      </c>
-      <c r="AJ3">
-        <v>0.2482993197278911</v>
-      </c>
-      <c r="AK3">
-        <v>0.2267080745341615</v>
-      </c>
-      <c r="AL3">
-        <v>0.313</v>
-      </c>
-      <c r="AM3">
-        <v>0.213</v>
-      </c>
-      <c r="AN3">
-        <v>-235.5555555555555</v>
-      </c>
-      <c r="AO3">
-        <v>-2.313099041533546</v>
-      </c>
-      <c r="AP3">
-        <v>-81.1111111111111</v>
-      </c>
-      <c r="AQ3">
-        <v>-3.39906103286385</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1112824707154981</v>
+      </c>
+      <c r="C4">
+        <v>37.30671476692408</v>
+      </c>
+      <c r="D4">
+        <v>28.63271476692408</v>
+      </c>
+      <c r="E4">
+        <v>-15.314</v>
+      </c>
+      <c r="F4">
+        <v>0.6859999999999999</v>
+      </c>
+      <c r="G4">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H4">
+        <v>18.3</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0.709</v>
+      </c>
+      <c r="K4">
+        <v>0.399</v>
+      </c>
+      <c r="L4">
+        <v>0.31</v>
+      </c>
+      <c r="M4">
+        <v>0.0350546</v>
+      </c>
+      <c r="N4">
+        <v>0.2749454</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0.2749454</v>
+      </c>
+      <c r="Q4">
+        <v>0.6739454</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1125106844035695</v>
+      </c>
+      <c r="T4">
+        <v>1.060765949179665</v>
+      </c>
+      <c r="U4">
+        <v>0.0511</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0511</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>8.843347235455546</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1115224707154981</v>
+      </c>
+      <c r="C5">
+        <v>36.86922056896228</v>
+      </c>
+      <c r="D5">
+        <v>28.53822056896228</v>
+      </c>
+      <c r="E5">
+        <v>-14.971</v>
+      </c>
+      <c r="F5">
+        <v>1.029</v>
+      </c>
+      <c r="G5">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H5">
+        <v>18.3</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0.709</v>
+      </c>
+      <c r="K5">
+        <v>0.399</v>
+      </c>
+      <c r="L5">
+        <v>0.31</v>
+      </c>
+      <c r="M5">
+        <v>0.05659499999999999</v>
+      </c>
+      <c r="N5">
+        <v>0.253405</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0.253405</v>
+      </c>
+      <c r="Q5">
+        <v>0.6524049999999999</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1132705883664929</v>
+      </c>
+      <c r="T5">
+        <v>1.071701680614506</v>
+      </c>
+      <c r="U5">
+        <v>0.055</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.055</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>5.477515681597315</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1120044707154981</v>
+      </c>
+      <c r="C6">
+        <v>36.33831643988663</v>
+      </c>
+      <c r="D6">
+        <v>28.35031643988662</v>
+      </c>
+      <c r="E6">
+        <v>-14.628</v>
+      </c>
+      <c r="F6">
+        <v>1.372</v>
+      </c>
+      <c r="G6">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H6">
+        <v>18.3</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0.709</v>
+      </c>
+      <c r="K6">
+        <v>0.399</v>
+      </c>
+      <c r="L6">
+        <v>0.31</v>
+      </c>
+      <c r="M6">
+        <v>0.086436</v>
+      </c>
+      <c r="N6">
+        <v>0.223564</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0.223564</v>
+      </c>
+      <c r="Q6">
+        <v>0.6225639999999999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1140463236619772</v>
+      </c>
+      <c r="T6">
+        <v>1.082865239787574</v>
+      </c>
+      <c r="U6">
+        <v>0.063</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.063</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>3.58646860104586</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1147214707154981</v>
+      </c>
+      <c r="C7">
+        <v>34.98074428998953</v>
+      </c>
+      <c r="D7">
+        <v>27.33574428998953</v>
+      </c>
+      <c r="E7">
+        <v>-14.285</v>
+      </c>
+      <c r="F7">
+        <v>1.715</v>
+      </c>
+      <c r="G7">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H7">
+        <v>18.3</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0.709</v>
+      </c>
+      <c r="K7">
+        <v>0.399</v>
+      </c>
+      <c r="L7">
+        <v>0.31</v>
+      </c>
+      <c r="M7">
+        <v>0.1929375</v>
+      </c>
+      <c r="N7">
+        <v>0.1170625</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0.1170625</v>
+      </c>
+      <c r="Q7">
+        <v>0.5160625</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1148383902268401</v>
+      </c>
+      <c r="T7">
+        <v>1.094263821259022</v>
+      </c>
+      <c r="U7">
+        <v>0.1125</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.1125</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>1.606737933268546</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1215364707154981</v>
+      </c>
+      <c r="C8">
+        <v>32.38610005468156</v>
+      </c>
+      <c r="D8">
+        <v>25.08410005468155</v>
+      </c>
+      <c r="E8">
+        <v>-13.942</v>
+      </c>
+      <c r="F8">
+        <v>2.058</v>
+      </c>
+      <c r="G8">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H8">
+        <v>18.3</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0.709</v>
+      </c>
+      <c r="K8">
+        <v>0.399</v>
+      </c>
+      <c r="L8">
+        <v>0.31</v>
+      </c>
+      <c r="M8">
+        <v>0.4400004</v>
+      </c>
+      <c r="N8">
+        <v>-0.1300004</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0.1300004</v>
+      </c>
+      <c r="Q8">
+        <v>0.2689996</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1156473092718065</v>
+      </c>
+      <c r="T8">
+        <v>1.105904925740501</v>
+      </c>
+      <c r="U8">
+        <v>0.2138</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.2138</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.7045448140501691</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1232864707154981</v>
+      </c>
+      <c r="C9">
+        <v>31.52352366897227</v>
+      </c>
+      <c r="D9">
+        <v>24.56452366897227</v>
+      </c>
+      <c r="E9">
+        <v>-13.599</v>
+      </c>
+      <c r="F9">
+        <v>2.401</v>
+      </c>
+      <c r="G9">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H9">
+        <v>18.3</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.709</v>
+      </c>
+      <c r="K9">
+        <v>0.399</v>
+      </c>
+      <c r="L9">
+        <v>0.31</v>
+      </c>
+      <c r="M9">
+        <v>0.5133338000000001</v>
+      </c>
+      <c r="N9">
+        <v>-0.2033338000000001</v>
+      </c>
+      <c r="O9">
+        <v>-0</v>
+      </c>
+      <c r="P9">
+        <v>-0.2033338000000001</v>
+      </c>
+      <c r="Q9">
+        <v>0.1956661999999999</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1164736244252668</v>
+      </c>
+      <c r="T9">
+        <v>1.117796376554915</v>
+      </c>
+      <c r="U9">
+        <v>0.2138</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.2138</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.6038955549001448</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1250364707154981</v>
+      </c>
+      <c r="C10">
+        <v>30.68203485021571</v>
+      </c>
+      <c r="D10">
+        <v>24.06603485021572</v>
+      </c>
+      <c r="E10">
+        <v>-13.256</v>
+      </c>
+      <c r="F10">
+        <v>2.744</v>
+      </c>
+      <c r="G10">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H10">
+        <v>18.3</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0.709</v>
+      </c>
+      <c r="K10">
+        <v>0.399</v>
+      </c>
+      <c r="L10">
+        <v>0.31</v>
+      </c>
+      <c r="M10">
+        <v>0.5866671999999999</v>
+      </c>
+      <c r="N10">
+        <v>-0.2766671999999999</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0.2766671999999999</v>
+      </c>
+      <c r="Q10">
+        <v>0.1223328</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1173179029516284</v>
+      </c>
+      <c r="T10">
+        <v>1.129946337169643</v>
+      </c>
+      <c r="U10">
+        <v>0.2138</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.2138</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.5284086105376269</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1290364707154981</v>
+      </c>
+      <c r="C11">
+        <v>29.27223626381744</v>
+      </c>
+      <c r="D11">
+        <v>22.99923626381744</v>
+      </c>
+      <c r="E11">
+        <v>-12.913</v>
+      </c>
+      <c r="F11">
+        <v>3.087</v>
+      </c>
+      <c r="G11">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H11">
+        <v>18.3</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.709</v>
+      </c>
+      <c r="K11">
+        <v>0.399</v>
+      </c>
+      <c r="L11">
+        <v>0.31</v>
+      </c>
+      <c r="M11">
+        <v>0.7371755999999999</v>
+      </c>
+      <c r="N11">
+        <v>-0.4271755999999999</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0.4271755999999999</v>
+      </c>
+      <c r="Q11">
+        <v>-0.02817559999999997</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1181807370499979</v>
+      </c>
+      <c r="T11">
+        <v>1.142363329885793</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.2388</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.4205239565715415</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1310364707154981</v>
+      </c>
+      <c r="C12">
+        <v>28.430534696305</v>
+      </c>
+      <c r="D12">
+        <v>22.500534696305</v>
+      </c>
+      <c r="E12">
+        <v>-12.57</v>
+      </c>
+      <c r="F12">
+        <v>3.43</v>
+      </c>
+      <c r="G12">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H12">
+        <v>18.3</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0.709</v>
+      </c>
+      <c r="K12">
+        <v>0.399</v>
+      </c>
+      <c r="L12">
+        <v>0.31</v>
+      </c>
+      <c r="M12">
+        <v>0.8190839999999999</v>
+      </c>
+      <c r="N12">
+        <v>-0.5090839999999999</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0.5090839999999999</v>
+      </c>
+      <c r="Q12">
+        <v>-0.1100839999999999</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1190627452394423</v>
+      </c>
+      <c r="T12">
+        <v>1.155056255773413</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.2388</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.3784715609143874</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1330364707154981</v>
+      </c>
+      <c r="C13">
+        <v>27.61000122066721</v>
+      </c>
+      <c r="D13">
+        <v>22.02300122066721</v>
+      </c>
+      <c r="E13">
+        <v>-12.227</v>
+      </c>
+      <c r="F13">
+        <v>3.773</v>
+      </c>
+      <c r="G13">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H13">
+        <v>18.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0.709</v>
+      </c>
+      <c r="K13">
+        <v>0.399</v>
+      </c>
+      <c r="L13">
+        <v>0.31</v>
+      </c>
+      <c r="M13">
+        <v>0.9009924</v>
+      </c>
+      <c r="N13">
+        <v>-0.5909924</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0.5909924</v>
+      </c>
+      <c r="Q13">
+        <v>-0.1919924</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1199645738376383</v>
+      </c>
+      <c r="T13">
+        <v>1.168034415950642</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.2388</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.3440650553767157</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1350364707154981</v>
+      </c>
+      <c r="C14">
+        <v>26.80931608203046</v>
+      </c>
+      <c r="D14">
+        <v>21.56531608203046</v>
+      </c>
+      <c r="E14">
+        <v>-11.884</v>
+      </c>
+      <c r="F14">
+        <v>4.116</v>
+      </c>
+      <c r="G14">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H14">
+        <v>18.3</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0.709</v>
+      </c>
+      <c r="K14">
+        <v>0.399</v>
+      </c>
+      <c r="L14">
+        <v>0.31</v>
+      </c>
+      <c r="M14">
+        <v>0.9829008</v>
+      </c>
+      <c r="N14">
+        <v>-0.6729008000000001</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0.6729008000000001</v>
+      </c>
+      <c r="Q14">
+        <v>-0.2739008000000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1208868985403387</v>
+      </c>
+      <c r="T14">
+        <v>1.181307534313717</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.2388</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.315392967428656</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1370364707154981</v>
+      </c>
+      <c r="C15">
+        <v>26.02726700127743</v>
+      </c>
+      <c r="D15">
+        <v>21.12626700127743</v>
+      </c>
+      <c r="E15">
+        <v>-11.541</v>
+      </c>
+      <c r="F15">
+        <v>4.459</v>
+      </c>
+      <c r="G15">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H15">
+        <v>18.3</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0.709</v>
+      </c>
+      <c r="K15">
+        <v>0.399</v>
+      </c>
+      <c r="L15">
+        <v>0.31</v>
+      </c>
+      <c r="M15">
+        <v>1.0648092</v>
+      </c>
+      <c r="N15">
+        <v>-0.7548092</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0.7548092</v>
+      </c>
+      <c r="Q15">
+        <v>-0.3558092</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1218304261097679</v>
+      </c>
+      <c r="T15">
+        <v>1.194885781834565</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.2388</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.2911319699341441</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1390364707154981</v>
+      </c>
+      <c r="C16">
+        <v>25.26273845282643</v>
+      </c>
+      <c r="D16">
+        <v>20.70473845282643</v>
+      </c>
+      <c r="E16">
+        <v>-11.198</v>
+      </c>
+      <c r="F16">
+        <v>4.802</v>
+      </c>
+      <c r="G16">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H16">
+        <v>18.3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0.709</v>
+      </c>
+      <c r="K16">
+        <v>0.399</v>
+      </c>
+      <c r="L16">
+        <v>0.31</v>
+      </c>
+      <c r="M16">
+        <v>1.1467176</v>
+      </c>
+      <c r="N16">
+        <v>-0.8367176000000001</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-0.8367176000000001</v>
+      </c>
+      <c r="Q16">
+        <v>-0.4377176000000001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1227958961808118</v>
+      </c>
+      <c r="T16">
+        <v>1.208779802553571</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.2388</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.2703368292245624</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1410364707154981</v>
+      </c>
+      <c r="C17">
+        <v>24.51470220093071</v>
+      </c>
+      <c r="D17">
+        <v>20.29970220093071</v>
+      </c>
+      <c r="E17">
+        <v>-10.855</v>
+      </c>
+      <c r="F17">
+        <v>5.145</v>
+      </c>
+      <c r="G17">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H17">
+        <v>18.3</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0.709</v>
+      </c>
+      <c r="K17">
+        <v>0.399</v>
+      </c>
+      <c r="L17">
+        <v>0.31</v>
+      </c>
+      <c r="M17">
+        <v>1.228626</v>
+      </c>
+      <c r="N17">
+        <v>-0.9186259999999999</v>
+      </c>
+      <c r="O17">
+        <v>-0</v>
+      </c>
+      <c r="P17">
+        <v>-0.9186259999999999</v>
+      </c>
+      <c r="Q17">
+        <v>-0.5196259999999999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1237840831947037</v>
+      </c>
+      <c r="T17">
+        <v>1.223000741407143</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.2388</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.2523143739429249</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1430364707154981</v>
+      </c>
+      <c r="C18">
+        <v>23.78220892546599</v>
+      </c>
+      <c r="D18">
+        <v>19.91020892546599</v>
+      </c>
+      <c r="E18">
+        <v>-10.512</v>
+      </c>
+      <c r="F18">
+        <v>5.488</v>
+      </c>
+      <c r="G18">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H18">
+        <v>18.3</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0.709</v>
+      </c>
+      <c r="K18">
+        <v>0.399</v>
+      </c>
+      <c r="L18">
+        <v>0.31</v>
+      </c>
+      <c r="M18">
+        <v>1.3105344</v>
+      </c>
+      <c r="N18">
+        <v>-1.0005344</v>
+      </c>
+      <c r="O18">
+        <v>-0</v>
+      </c>
+      <c r="P18">
+        <v>-1.0005344</v>
+      </c>
+      <c r="Q18">
+        <v>-0.6015343999999998</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1247957984708311</v>
+      </c>
+      <c r="T18">
+        <v>1.237560274042942</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.2388</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.2365447255714921</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1450364707154981</v>
+      </c>
+      <c r="C19">
+        <v>23.06438079363195</v>
+      </c>
+      <c r="D19">
+        <v>19.53538079363195</v>
+      </c>
+      <c r="E19">
+        <v>-10.169</v>
+      </c>
+      <c r="F19">
+        <v>5.831</v>
+      </c>
+      <c r="G19">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H19">
+        <v>18.3</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0.709</v>
+      </c>
+      <c r="K19">
+        <v>0.399</v>
+      </c>
+      <c r="L19">
+        <v>0.31</v>
+      </c>
+      <c r="M19">
+        <v>1.3924428</v>
+      </c>
+      <c r="N19">
+        <v>-1.0824428</v>
+      </c>
+      <c r="O19">
+        <v>-0</v>
+      </c>
+      <c r="P19">
+        <v>-1.0824428</v>
+      </c>
+      <c r="Q19">
+        <v>-0.6834427999999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.125831892428311</v>
+      </c>
+      <c r="T19">
+        <v>1.252470638790447</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.2388</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.2226303299496396</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1470364707154981</v>
+      </c>
+      <c r="C20">
+        <v>22.36040485521686</v>
+      </c>
+      <c r="D20">
+        <v>19.17440485521686</v>
+      </c>
+      <c r="E20">
+        <v>-9.826000000000001</v>
+      </c>
+      <c r="F20">
+        <v>6.173999999999999</v>
+      </c>
+      <c r="G20">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H20">
+        <v>18.3</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0.709</v>
+      </c>
+      <c r="K20">
+        <v>0.399</v>
+      </c>
+      <c r="L20">
+        <v>0.31</v>
+      </c>
+      <c r="M20">
+        <v>1.4743512</v>
+      </c>
+      <c r="N20">
+        <v>-1.1643512</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-1.1643512</v>
+      </c>
+      <c r="Q20">
+        <v>-0.7653511999999998</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1268932569701197</v>
+      </c>
+      <c r="T20">
+        <v>1.267744670970819</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.2388</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.2102619782857708</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1490364707154981</v>
+      </c>
+      <c r="C21">
+        <v>21.66952715683331</v>
+      </c>
+      <c r="D21">
+        <v>18.82652715683331</v>
+      </c>
+      <c r="E21">
+        <v>-9.483000000000001</v>
+      </c>
+      <c r="F21">
+        <v>6.516999999999999</v>
+      </c>
+      <c r="G21">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H21">
+        <v>18.3</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0.709</v>
+      </c>
+      <c r="K21">
+        <v>0.399</v>
+      </c>
+      <c r="L21">
+        <v>0.31</v>
+      </c>
+      <c r="M21">
+        <v>1.5562596</v>
+      </c>
+      <c r="N21">
+        <v>-1.2462596</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-1.2462596</v>
+      </c>
+      <c r="Q21">
+        <v>-0.8472595999999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1279808280438248</v>
+      </c>
+      <c r="T21">
+        <v>1.283395839748236</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.2388</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.1991955583759933</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1510364707154981</v>
+      </c>
+      <c r="C22">
+        <v>20.99104748544279</v>
+      </c>
+      <c r="D22">
+        <v>18.49104748544279</v>
+      </c>
+      <c r="E22">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="F22">
+        <v>6.859999999999999</v>
+      </c>
+      <c r="G22">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H22">
+        <v>18.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0.709</v>
+      </c>
+      <c r="K22">
+        <v>0.399</v>
+      </c>
+      <c r="L22">
+        <v>0.31</v>
+      </c>
+      <c r="M22">
+        <v>1.638168</v>
+      </c>
+      <c r="N22">
+        <v>-1.328168</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-1.328168</v>
+      </c>
+      <c r="Q22">
+        <v>-0.9291679999999998</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1290955883943726</v>
+      </c>
+      <c r="T22">
+        <v>1.299438287745089</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.2388</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.1892357804571937</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1530364707154981</v>
+      </c>
+      <c r="C23">
+        <v>20.32431466404823</v>
+      </c>
+      <c r="D23">
+        <v>18.16731466404823</v>
+      </c>
+      <c r="E23">
+        <v>-8.797000000000001</v>
+      </c>
+      <c r="F23">
+        <v>7.202999999999999</v>
+      </c>
+      <c r="G23">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H23">
+        <v>18.3</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0.709</v>
+      </c>
+      <c r="K23">
+        <v>0.399</v>
+      </c>
+      <c r="L23">
+        <v>0.31</v>
+      </c>
+      <c r="M23">
+        <v>1.7200764</v>
+      </c>
+      <c r="N23">
+        <v>-1.4100764</v>
+      </c>
+      <c r="O23">
+        <v>-0</v>
+      </c>
+      <c r="P23">
+        <v>-1.4100764</v>
+      </c>
+      <c r="Q23">
+        <v>-1.0110764</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.130238570525947</v>
+      </c>
+      <c r="T23">
+        <v>1.315886873665913</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.2388</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.1802245528163749</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1550364707154981</v>
+      </c>
+      <c r="C24">
+        <v>19.66872233304887</v>
+      </c>
+      <c r="D24">
+        <v>17.85472233304887</v>
+      </c>
+      <c r="E24">
+        <v>-8.454000000000001</v>
+      </c>
+      <c r="F24">
+        <v>7.545999999999999</v>
+      </c>
+      <c r="G24">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H24">
+        <v>18.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0.709</v>
+      </c>
+      <c r="K24">
+        <v>0.399</v>
+      </c>
+      <c r="L24">
+        <v>0.31</v>
+      </c>
+      <c r="M24">
+        <v>1.8019848</v>
+      </c>
+      <c r="N24">
+        <v>-1.4919848</v>
+      </c>
+      <c r="O24">
+        <v>-0</v>
+      </c>
+      <c r="P24">
+        <v>-1.4919848</v>
+      </c>
+      <c r="Q24">
+        <v>-1.0929848</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1314108598916642</v>
+      </c>
+      <c r="T24">
+        <v>1.332757218200091</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.2388</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.1720325276883579</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1570364707154981</v>
+      </c>
+      <c r="C25">
+        <v>19.02370515975196</v>
+      </c>
+      <c r="D25">
+        <v>17.55270515975196</v>
+      </c>
+      <c r="E25">
+        <v>-8.111000000000001</v>
+      </c>
+      <c r="F25">
+        <v>7.888999999999999</v>
+      </c>
+      <c r="G25">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H25">
+        <v>18.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0.709</v>
+      </c>
+      <c r="K25">
+        <v>0.399</v>
+      </c>
+      <c r="L25">
+        <v>0.31</v>
+      </c>
+      <c r="M25">
+        <v>1.8838932</v>
+      </c>
+      <c r="N25">
+        <v>-1.5738932</v>
+      </c>
+      <c r="O25">
+        <v>-0</v>
+      </c>
+      <c r="P25">
+        <v>-1.5738932</v>
+      </c>
+      <c r="Q25">
+        <v>-1.1748932</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1326135983318157</v>
+      </c>
+      <c r="T25">
+        <v>1.350065753501391</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.2388</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.1645528525714728</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1590364707154981</v>
+      </c>
+      <c r="C26">
+        <v>18.38873542618775</v>
+      </c>
+      <c r="D26">
+        <v>17.26073542618775</v>
+      </c>
+      <c r="E26">
+        <v>-7.768000000000001</v>
+      </c>
+      <c r="F26">
+        <v>8.231999999999999</v>
+      </c>
+      <c r="G26">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H26">
+        <v>18.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0.709</v>
+      </c>
+      <c r="K26">
+        <v>0.399</v>
+      </c>
+      <c r="L26">
+        <v>0.31</v>
+      </c>
+      <c r="M26">
+        <v>1.9658016</v>
+      </c>
+      <c r="N26">
+        <v>-1.6558016</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-1.6558016</v>
+      </c>
+      <c r="Q26">
+        <v>-1.2568016</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1338479877835502</v>
+      </c>
+      <c r="T26">
+        <v>1.367829776573778</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.2388</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.1576964837143281</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1610364707154981</v>
+      </c>
+      <c r="C27">
+        <v>17.76331995190003</v>
+      </c>
+      <c r="D27">
+        <v>16.97831995190003</v>
+      </c>
+      <c r="E27">
+        <v>-7.425000000000001</v>
+      </c>
+      <c r="F27">
+        <v>8.574999999999999</v>
+      </c>
+      <c r="G27">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H27">
+        <v>18.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0.709</v>
+      </c>
+      <c r="K27">
+        <v>0.399</v>
+      </c>
+      <c r="L27">
+        <v>0.31</v>
+      </c>
+      <c r="M27">
+        <v>2.04771</v>
+      </c>
+      <c r="N27">
+        <v>-1.73771</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-1.73771</v>
+      </c>
+      <c r="Q27">
+        <v>-1.33871</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1351152942873308</v>
+      </c>
+      <c r="T27">
+        <v>1.386067506928095</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.2388</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.151388624365755</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1630364707154981</v>
+      </c>
+      <c r="C28">
+        <v>17.14699731396418</v>
+      </c>
+      <c r="D28">
+        <v>16.70499731396418</v>
+      </c>
+      <c r="E28">
+        <v>-7.082000000000001</v>
+      </c>
+      <c r="F28">
+        <v>8.917999999999999</v>
+      </c>
+      <c r="G28">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H28">
+        <v>18.3</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0.709</v>
+      </c>
+      <c r="K28">
+        <v>0.399</v>
+      </c>
+      <c r="L28">
+        <v>0.31</v>
+      </c>
+      <c r="M28">
+        <v>2.1296184</v>
+      </c>
+      <c r="N28">
+        <v>-1.8196184</v>
+      </c>
+      <c r="O28">
+        <v>-0</v>
+      </c>
+      <c r="P28">
+        <v>-1.8196184</v>
+      </c>
+      <c r="Q28">
+        <v>-1.4206184</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1364168523182407</v>
+      </c>
+      <c r="T28">
+        <v>1.40479814891361</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.2388</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.1455659849670721</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1650364707154981</v>
+      </c>
+      <c r="C29">
+        <v>16.53933533126961</v>
+      </c>
+      <c r="D29">
+        <v>16.44033533126961</v>
+      </c>
+      <c r="E29">
+        <v>-6.739000000000001</v>
+      </c>
+      <c r="F29">
+        <v>9.260999999999999</v>
+      </c>
+      <c r="G29">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H29">
+        <v>18.3</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0.709</v>
+      </c>
+      <c r="K29">
+        <v>0.399</v>
+      </c>
+      <c r="L29">
+        <v>0.31</v>
+      </c>
+      <c r="M29">
+        <v>2.2115268</v>
+      </c>
+      <c r="N29">
+        <v>-1.9015268</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-1.9015268</v>
+      </c>
+      <c r="Q29">
+        <v>-1.5025268</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1377540694732851</v>
+      </c>
+      <c r="T29">
+        <v>1.4240419591727</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.2388</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.1401746521905138</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1670364707154981</v>
+      </c>
+      <c r="C30">
+        <v>15.93992878421571</v>
+      </c>
+      <c r="D30">
+        <v>16.18392878421571</v>
+      </c>
+      <c r="E30">
+        <v>-6.395999999999999</v>
+      </c>
+      <c r="F30">
+        <v>9.604000000000001</v>
+      </c>
+      <c r="G30">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H30">
+        <v>18.3</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0.709</v>
+      </c>
+      <c r="K30">
+        <v>0.399</v>
+      </c>
+      <c r="L30">
+        <v>0.31</v>
+      </c>
+      <c r="M30">
+        <v>2.2934352</v>
+      </c>
+      <c r="N30">
+        <v>-1.9834352</v>
+      </c>
+      <c r="O30">
+        <v>-0</v>
+      </c>
+      <c r="P30">
+        <v>-1.9834352</v>
+      </c>
+      <c r="Q30">
+        <v>-1.5844352</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1391284315493029</v>
+      </c>
+      <c r="T30">
+        <v>1.443820319716766</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.2388</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.1351684146122812</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1690364707154981</v>
+      </c>
+      <c r="C31">
+        <v>15.34839734451524</v>
+      </c>
+      <c r="D31">
+        <v>15.93539734451524</v>
+      </c>
+      <c r="E31">
+        <v>-6.053000000000001</v>
+      </c>
+      <c r="F31">
+        <v>9.946999999999999</v>
+      </c>
+      <c r="G31">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H31">
+        <v>18.3</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0.709</v>
+      </c>
+      <c r="K31">
+        <v>0.399</v>
+      </c>
+      <c r="L31">
+        <v>0.31</v>
+      </c>
+      <c r="M31">
+        <v>2.3753436</v>
+      </c>
+      <c r="N31">
+        <v>-2.0653436</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-2.0653436</v>
+      </c>
+      <c r="Q31">
+        <v>-1.6663436</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1405415080499973</v>
+      </c>
+      <c r="T31">
+        <v>1.464155817177565</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.2388</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.1305074347980646</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1710364707154981</v>
+      </c>
+      <c r="C32">
+        <v>14.76438369286085</v>
+      </c>
+      <c r="D32">
+        <v>15.69438369286085</v>
+      </c>
+      <c r="E32">
+        <v>-5.710000000000001</v>
+      </c>
+      <c r="F32">
+        <v>10.29</v>
+      </c>
+      <c r="G32">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H32">
+        <v>18.3</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0.709</v>
+      </c>
+      <c r="K32">
+        <v>0.399</v>
+      </c>
+      <c r="L32">
+        <v>0.31</v>
+      </c>
+      <c r="M32">
+        <v>2.457252</v>
+      </c>
+      <c r="N32">
+        <v>-2.147252</v>
+      </c>
+      <c r="O32">
+        <v>-0</v>
+      </c>
+      <c r="P32">
+        <v>-2.147252</v>
+      </c>
+      <c r="Q32">
+        <v>-1.748252</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1419949581649973</v>
+      </c>
+      <c r="T32">
+        <v>1.48507232885153</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.2388</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.1261571869714625</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1730364707154981</v>
+      </c>
+      <c r="C33">
+        <v>14.18755180486189</v>
+      </c>
+      <c r="D33">
+        <v>15.46055180486189</v>
+      </c>
+      <c r="E33">
+        <v>-5.367000000000001</v>
+      </c>
+      <c r="F33">
+        <v>10.633</v>
+      </c>
+      <c r="G33">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H33">
+        <v>18.3</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0.709</v>
+      </c>
+      <c r="K33">
+        <v>0.399</v>
+      </c>
+      <c r="L33">
+        <v>0.31</v>
+      </c>
+      <c r="M33">
+        <v>2.5391604</v>
+      </c>
+      <c r="N33">
+        <v>-2.2291604</v>
+      </c>
+      <c r="O33">
+        <v>-0</v>
+      </c>
+      <c r="P33">
+        <v>-2.2291604</v>
+      </c>
+      <c r="Q33">
+        <v>-1.8301604</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1434905372688378</v>
+      </c>
+      <c r="T33">
+        <v>1.50659511622619</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.2388</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.1220876002949637</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1750364707154981</v>
+      </c>
+      <c r="C34">
+        <v>13.61758538795951</v>
+      </c>
+      <c r="D34">
+        <v>15.23358538795951</v>
+      </c>
+      <c r="E34">
+        <v>-5.024000000000001</v>
+      </c>
+      <c r="F34">
+        <v>10.976</v>
+      </c>
+      <c r="G34">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H34">
+        <v>18.3</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0.709</v>
+      </c>
+      <c r="K34">
+        <v>0.399</v>
+      </c>
+      <c r="L34">
+        <v>0.31</v>
+      </c>
+      <c r="M34">
+        <v>2.6210688</v>
+      </c>
+      <c r="N34">
+        <v>-2.3110688</v>
+      </c>
+      <c r="O34">
+        <v>-0</v>
+      </c>
+      <c r="P34">
+        <v>-2.3110688</v>
+      </c>
+      <c r="Q34">
+        <v>-1.9120688</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1450301039933796</v>
+      </c>
+      <c r="T34">
+        <v>1.528750926758929</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.2388</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.118272362785746</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1770364707154981</v>
+      </c>
+      <c r="C35">
+        <v>13.05418645402967</v>
+      </c>
+      <c r="D35">
+        <v>15.01318645402966</v>
+      </c>
+      <c r="E35">
+        <v>-4.681000000000001</v>
+      </c>
+      <c r="F35">
+        <v>11.319</v>
+      </c>
+      <c r="G35">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H35">
+        <v>18.3</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0.709</v>
+      </c>
+      <c r="K35">
+        <v>0.399</v>
+      </c>
+      <c r="L35">
+        <v>0.31</v>
+      </c>
+      <c r="M35">
+        <v>2.7029772</v>
+      </c>
+      <c r="N35">
+        <v>-2.3929772</v>
+      </c>
+      <c r="O35">
+        <v>-0</v>
+      </c>
+      <c r="P35">
+        <v>-2.3929772</v>
+      </c>
+      <c r="Q35">
+        <v>-1.9939772</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1466156279335793</v>
+      </c>
+      <c r="T35">
+        <v>1.551568104770256</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.2388</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.1146883517922386</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1790364707154981</v>
+      </c>
+      <c r="C36">
+        <v>12.49707401412824</v>
+      </c>
+      <c r="D36">
+        <v>14.79907401412825</v>
+      </c>
+      <c r="E36">
+        <v>-4.338000000000001</v>
+      </c>
+      <c r="F36">
+        <v>11.662</v>
+      </c>
+      <c r="G36">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H36">
+        <v>18.3</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0.709</v>
+      </c>
+      <c r="K36">
+        <v>0.399</v>
+      </c>
+      <c r="L36">
+        <v>0.31</v>
+      </c>
+      <c r="M36">
+        <v>2.7848856</v>
+      </c>
+      <c r="N36">
+        <v>-2.4748856</v>
+      </c>
+      <c r="O36">
+        <v>-0</v>
+      </c>
+      <c r="P36">
+        <v>-2.4748856</v>
+      </c>
+      <c r="Q36">
+        <v>-2.0758856</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.148249198053785</v>
+      </c>
+      <c r="T36">
+        <v>1.57507671241829</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.2388</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.1113151649748199</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1810364707154981</v>
+      </c>
+      <c r="C37">
+        <v>11.94598288335589</v>
+      </c>
+      <c r="D37">
+        <v>14.5909828833559</v>
+      </c>
+      <c r="E37">
+        <v>-3.994999999999999</v>
+      </c>
+      <c r="F37">
+        <v>12.005</v>
+      </c>
+      <c r="G37">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H37">
+        <v>18.3</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0.709</v>
+      </c>
+      <c r="K37">
+        <v>0.399</v>
+      </c>
+      <c r="L37">
+        <v>0.31</v>
+      </c>
+      <c r="M37">
+        <v>2.866794000000001</v>
+      </c>
+      <c r="N37">
+        <v>-2.556794</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-2.556794</v>
+      </c>
+      <c r="Q37">
+        <v>-2.157794</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1499330318699971</v>
+      </c>
+      <c r="T37">
+        <v>1.59930866184011</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.2388</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.1081347316898249</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1830364707154981</v>
+      </c>
+      <c r="C38">
+        <v>11.40066258515425</v>
+      </c>
+      <c r="D38">
+        <v>14.38866258515425</v>
+      </c>
+      <c r="E38">
+        <v>-3.652000000000001</v>
+      </c>
+      <c r="F38">
+        <v>12.348</v>
+      </c>
+      <c r="G38">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H38">
+        <v>18.3</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0.709</v>
+      </c>
+      <c r="K38">
+        <v>0.399</v>
+      </c>
+      <c r="L38">
+        <v>0.31</v>
+      </c>
+      <c r="M38">
+        <v>2.9487024</v>
+      </c>
+      <c r="N38">
+        <v>-2.6387024</v>
+      </c>
+      <c r="O38">
+        <v>-0</v>
+      </c>
+      <c r="P38">
+        <v>-2.6387024</v>
+      </c>
+      <c r="Q38">
+        <v>-2.2397024</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1516694854929658</v>
+      </c>
+      <c r="T38">
+        <v>1.624297859681361</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.2388</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.1051309891428854</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1850364707154981</v>
+      </c>
+      <c r="C39">
+        <v>10.86087634551439</v>
+      </c>
+      <c r="D39">
+        <v>14.19187634551439</v>
+      </c>
+      <c r="E39">
+        <v>-3.309000000000001</v>
+      </c>
+      <c r="F39">
+        <v>12.691</v>
+      </c>
+      <c r="G39">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H39">
+        <v>18.3</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0.709</v>
+      </c>
+      <c r="K39">
+        <v>0.399</v>
+      </c>
+      <c r="L39">
+        <v>0.31</v>
+      </c>
+      <c r="M39">
+        <v>3.0306108</v>
+      </c>
+      <c r="N39">
+        <v>-2.7206108</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-2.7206108</v>
+      </c>
+      <c r="Q39">
+        <v>-2.3216108</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1534610646277748</v>
+      </c>
+      <c r="T39">
+        <v>1.65008036539059</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.2388</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.1022896110579425</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1870364707154981</v>
+      </c>
+      <c r="C40">
+        <v>10.32640016860578</v>
+      </c>
+      <c r="D40">
+        <v>14.00040016860578</v>
+      </c>
+      <c r="E40">
+        <v>-2.966000000000001</v>
+      </c>
+      <c r="F40">
+        <v>13.034</v>
+      </c>
+      <c r="G40">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H40">
+        <v>18.3</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0.709</v>
+      </c>
+      <c r="K40">
+        <v>0.399</v>
+      </c>
+      <c r="L40">
+        <v>0.31</v>
+      </c>
+      <c r="M40">
+        <v>3.1125192</v>
+      </c>
+      <c r="N40">
+        <v>-2.8025192</v>
+      </c>
+      <c r="O40">
+        <v>-0</v>
+      </c>
+      <c r="P40">
+        <v>-2.8025192</v>
+      </c>
+      <c r="Q40">
+        <v>-2.4035192</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1553104366379002</v>
+      </c>
+      <c r="T40">
+        <v>1.676694564832373</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.2388</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.09959777918799673</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1890364707154981</v>
+      </c>
+      <c r="C41">
+        <v>9.797021986238615</v>
+      </c>
+      <c r="D41">
+        <v>13.81402198623862</v>
+      </c>
+      <c r="E41">
+        <v>-2.623000000000001</v>
+      </c>
+      <c r="F41">
+        <v>13.377</v>
+      </c>
+      <c r="G41">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H41">
+        <v>18.3</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0.709</v>
+      </c>
+      <c r="K41">
+        <v>0.399</v>
+      </c>
+      <c r="L41">
+        <v>0.31</v>
+      </c>
+      <c r="M41">
+        <v>3.1944276</v>
+      </c>
+      <c r="N41">
+        <v>-2.8844276</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-2.8844276</v>
+      </c>
+      <c r="Q41">
+        <v>-2.4854276</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1572204437958986</v>
+      </c>
+      <c r="T41">
+        <v>1.704181360977166</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.2388</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.09704398997804808</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1910364707154981</v>
+      </c>
+      <c r="C42">
+        <v>9.272540874369511</v>
+      </c>
+      <c r="D42">
+        <v>13.63254087436951</v>
+      </c>
+      <c r="E42">
+        <v>-2.280000000000001</v>
+      </c>
+      <c r="F42">
+        <v>13.72</v>
+      </c>
+      <c r="G42">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H42">
+        <v>18.3</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0.709</v>
+      </c>
+      <c r="K42">
+        <v>0.399</v>
+      </c>
+      <c r="L42">
+        <v>0.31</v>
+      </c>
+      <c r="M42">
+        <v>3.276336</v>
+      </c>
+      <c r="N42">
+        <v>-2.966336</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-2.966336</v>
+      </c>
+      <c r="Q42">
+        <v>-2.567336</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1591941178591635</v>
+      </c>
+      <c r="T42">
+        <v>1.732584383660119</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.2388</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.0946178902285969</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1930364707154981</v>
+      </c>
+      <c r="C43">
+        <v>8.752766330565072</v>
+      </c>
+      <c r="D43">
+        <v>13.45576633056507</v>
+      </c>
+      <c r="E43">
+        <v>-1.936999999999999</v>
+      </c>
+      <c r="F43">
+        <v>14.063</v>
+      </c>
+      <c r="G43">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H43">
+        <v>18.3</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0.709</v>
+      </c>
+      <c r="K43">
+        <v>0.399</v>
+      </c>
+      <c r="L43">
+        <v>0.31</v>
+      </c>
+      <c r="M43">
+        <v>3.3582444</v>
+      </c>
+      <c r="N43">
+        <v>-3.0482444</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-3.0482444</v>
+      </c>
+      <c r="Q43">
+        <v>-2.6492444</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1612346961279629</v>
+      </c>
+      <c r="T43">
+        <v>1.761950220671307</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2388</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.09231013680838718</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1950364707154981</v>
+      </c>
+      <c r="C44">
+        <v>8.23751760696112</v>
+      </c>
+      <c r="D44">
+        <v>13.28351760696112</v>
+      </c>
+      <c r="E44">
+        <v>-1.594000000000001</v>
+      </c>
+      <c r="F44">
+        <v>14.406</v>
+      </c>
+      <c r="G44">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H44">
+        <v>18.3</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0.709</v>
+      </c>
+      <c r="K44">
+        <v>0.399</v>
+      </c>
+      <c r="L44">
+        <v>0.31</v>
+      </c>
+      <c r="M44">
+        <v>3.4401528</v>
+      </c>
+      <c r="N44">
+        <v>-3.1301528</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-3.1301528</v>
+      </c>
+      <c r="Q44">
+        <v>-2.7311528</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1633456391646519</v>
+      </c>
+      <c r="T44">
+        <v>1.792328672751847</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2388</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.09011227640818742</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1970364707154981</v>
+      </c>
+      <c r="C45">
+        <v>7.726623093807522</v>
+      </c>
+      <c r="D45">
+        <v>13.11562309380752</v>
+      </c>
+      <c r="E45">
+        <v>-1.251000000000001</v>
+      </c>
+      <c r="F45">
+        <v>14.749</v>
+      </c>
+      <c r="G45">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H45">
+        <v>18.3</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0.709</v>
+      </c>
+      <c r="K45">
+        <v>0.399</v>
+      </c>
+      <c r="L45">
+        <v>0.31</v>
+      </c>
+      <c r="M45">
+        <v>3.5220612</v>
+      </c>
+      <c r="N45">
+        <v>-3.2120612</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-3.2120612</v>
+      </c>
+      <c r="Q45">
+        <v>-2.8130612</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1655306503780669</v>
+      </c>
+      <c r="T45">
+        <v>1.823773035431704</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2388</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.08801664207311333</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1990364707154981</v>
+      </c>
+      <c r="C46">
+        <v>7.219919749178889</v>
+      </c>
+      <c r="D46">
+        <v>12.95191974917889</v>
+      </c>
+      <c r="E46">
+        <v>-0.9080000000000013</v>
+      </c>
+      <c r="F46">
+        <v>15.092</v>
+      </c>
+      <c r="G46">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H46">
+        <v>18.3</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0.709</v>
+      </c>
+      <c r="K46">
+        <v>0.399</v>
+      </c>
+      <c r="L46">
+        <v>0.31</v>
+      </c>
+      <c r="M46">
+        <v>3.6039696</v>
+      </c>
+      <c r="N46">
+        <v>-3.2939696</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-3.2939696</v>
+      </c>
+      <c r="Q46">
+        <v>-2.8949696</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1677936977062466</v>
+      </c>
+      <c r="T46">
+        <v>1.856340411064413</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2388</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.08601626384417893</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2010364707154981</v>
+      </c>
+      <c r="C47">
+        <v>6.717252570867405</v>
+      </c>
+      <c r="D47">
+        <v>12.7922525708674</v>
+      </c>
+      <c r="E47">
+        <v>-0.5650000000000013</v>
+      </c>
+      <c r="F47">
+        <v>15.435</v>
+      </c>
+      <c r="G47">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H47">
+        <v>18.3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0.709</v>
+      </c>
+      <c r="K47">
+        <v>0.399</v>
+      </c>
+      <c r="L47">
+        <v>0.31</v>
+      </c>
+      <c r="M47">
+        <v>3.685878</v>
+      </c>
+      <c r="N47">
+        <v>-3.375878</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-3.375878</v>
+      </c>
+      <c r="Q47">
+        <v>-2.976878</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.170139037664542</v>
+      </c>
+      <c r="T47">
+        <v>1.890092054901948</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2388</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.08410479131430826</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2030364707154981</v>
+      </c>
+      <c r="C48">
+        <v>6.218474106861962</v>
+      </c>
+      <c r="D48">
+        <v>12.63647410686196</v>
+      </c>
+      <c r="E48">
+        <v>-0.2220000000000013</v>
+      </c>
+      <c r="F48">
+        <v>15.778</v>
+      </c>
+      <c r="G48">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H48">
+        <v>18.3</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0.709</v>
+      </c>
+      <c r="K48">
+        <v>0.399</v>
+      </c>
+      <c r="L48">
+        <v>0.31</v>
+      </c>
+      <c r="M48">
+        <v>3.7677864</v>
+      </c>
+      <c r="N48">
+        <v>-3.4577864</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-3.4577864</v>
+      </c>
+      <c r="Q48">
+        <v>-3.0587864</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1725712420657372</v>
+      </c>
+      <c r="T48">
+        <v>1.925093759622354</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2388</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.08227642628573639</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2050364707154981</v>
+      </c>
+      <c r="C49">
+        <v>5.723444001164058</v>
+      </c>
+      <c r="D49">
+        <v>12.48444400116406</v>
+      </c>
+      <c r="E49">
+        <v>0.1209999999999987</v>
+      </c>
+      <c r="F49">
+        <v>16.121</v>
+      </c>
+      <c r="G49">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H49">
+        <v>18.3</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0.709</v>
+      </c>
+      <c r="K49">
+        <v>0.399</v>
+      </c>
+      <c r="L49">
+        <v>0.31</v>
+      </c>
+      <c r="M49">
+        <v>3.8496948</v>
+      </c>
+      <c r="N49">
+        <v>-3.5396948</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-3.5396948</v>
+      </c>
+      <c r="Q49">
+        <v>-3.1406948</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1750952277650908</v>
+      </c>
+      <c r="T49">
+        <v>1.961416283388814</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2388</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.0805258640243377</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2070364707154981</v>
+      </c>
+      <c r="C50">
+        <v>5.232028571999756</v>
+      </c>
+      <c r="D50">
+        <v>12.33602857199976</v>
+      </c>
+      <c r="E50">
+        <v>0.4639999999999986</v>
+      </c>
+      <c r="F50">
+        <v>16.464</v>
+      </c>
+      <c r="G50">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H50">
+        <v>18.3</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0.709</v>
+      </c>
+      <c r="K50">
+        <v>0.399</v>
+      </c>
+      <c r="L50">
+        <v>0.31</v>
+      </c>
+      <c r="M50">
+        <v>3.9316032</v>
+      </c>
+      <c r="N50">
+        <v>-3.6216032</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-3.6216032</v>
+      </c>
+      <c r="Q50">
+        <v>-3.2226032</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1777162898374963</v>
+      </c>
+      <c r="T50">
+        <v>1.999135827300137</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2388</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.07884824185716399</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2090364707154981</v>
+      </c>
+      <c r="C51">
+        <v>4.744100419763615</v>
+      </c>
+      <c r="D51">
+        <v>12.19110041976361</v>
+      </c>
+      <c r="E51">
+        <v>0.8069999999999986</v>
+      </c>
+      <c r="F51">
+        <v>16.807</v>
+      </c>
+      <c r="G51">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H51">
+        <v>18.3</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0.709</v>
+      </c>
+      <c r="K51">
+        <v>0.399</v>
+      </c>
+      <c r="L51">
+        <v>0.31</v>
+      </c>
+      <c r="M51">
+        <v>4.0135116</v>
+      </c>
+      <c r="N51">
+        <v>-3.7035116</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-3.7035116</v>
+      </c>
+      <c r="Q51">
+        <v>-3.3045116</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1804401386578394</v>
+      </c>
+      <c r="T51">
+        <v>2.038334569011905</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2388</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.07723909406416063</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2110364707154981</v>
+      </c>
+      <c r="C52">
+        <v>4.25953806227777</v>
+      </c>
+      <c r="D52">
+        <v>12.04953806227777</v>
+      </c>
+      <c r="E52">
+        <v>1.149999999999999</v>
+      </c>
+      <c r="F52">
+        <v>17.15</v>
+      </c>
+      <c r="G52">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H52">
+        <v>18.3</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0.709</v>
+      </c>
+      <c r="K52">
+        <v>0.399</v>
+      </c>
+      <c r="L52">
+        <v>0.31</v>
+      </c>
+      <c r="M52">
+        <v>4.09542</v>
+      </c>
+      <c r="N52">
+        <v>-3.78542</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-3.78542</v>
+      </c>
+      <c r="Q52">
+        <v>-3.38642</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1832729414309962</v>
+      </c>
+      <c r="T52">
+        <v>2.079101260392143</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2388</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.07569431218287748</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2130364707154981</v>
+      </c>
+      <c r="C53">
+        <v>3.778225595171467</v>
+      </c>
+      <c r="D53">
+        <v>11.91122559517147</v>
+      </c>
+      <c r="E53">
+        <v>1.492999999999999</v>
+      </c>
+      <c r="F53">
+        <v>17.493</v>
+      </c>
+      <c r="G53">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H53">
+        <v>18.3</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0.709</v>
+      </c>
+      <c r="K53">
+        <v>0.399</v>
+      </c>
+      <c r="L53">
+        <v>0.31</v>
+      </c>
+      <c r="M53">
+        <v>4.177328399999999</v>
+      </c>
+      <c r="N53">
+        <v>-3.867328399999999</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-3.867328399999999</v>
+      </c>
+      <c r="Q53">
+        <v>-3.468328399999999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.186221368807139</v>
+      </c>
+      <c r="T53">
+        <v>2.121531898359329</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2388</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.0742101099832132</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2150364707154981</v>
+      </c>
+      <c r="C54">
+        <v>3.30005237538542</v>
+      </c>
+      <c r="D54">
+        <v>11.77605237538542</v>
+      </c>
+      <c r="E54">
+        <v>1.835999999999999</v>
+      </c>
+      <c r="F54">
+        <v>17.836</v>
+      </c>
+      <c r="G54">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H54">
+        <v>18.3</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0.709</v>
+      </c>
+      <c r="K54">
+        <v>0.399</v>
+      </c>
+      <c r="L54">
+        <v>0.31</v>
+      </c>
+      <c r="M54">
+        <v>4.2592368</v>
+      </c>
+      <c r="N54">
+        <v>-3.9492368</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-3.9492368</v>
+      </c>
+      <c r="Q54">
+        <v>-3.5502368</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1892926473239544</v>
+      </c>
+      <c r="T54">
+        <v>2.165730479575149</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2388</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.07278299248353604</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2170364707154981</v>
+      </c>
+      <c r="C55">
+        <v>2.824912725984685</v>
+      </c>
+      <c r="D55">
+        <v>11.64391272598468</v>
+      </c>
+      <c r="E55">
+        <v>2.178999999999998</v>
+      </c>
+      <c r="F55">
+        <v>18.179</v>
+      </c>
+      <c r="G55">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H55">
+        <v>18.3</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0.709</v>
+      </c>
+      <c r="K55">
+        <v>0.399</v>
+      </c>
+      <c r="L55">
+        <v>0.31</v>
+      </c>
+      <c r="M55">
+        <v>4.3411452</v>
+      </c>
+      <c r="N55">
+        <v>-4.0311452</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-4.0311452</v>
+      </c>
+      <c r="Q55">
+        <v>-3.6321452</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.192494618543613</v>
+      </c>
+      <c r="T55">
+        <v>2.211809851481003</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2388</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.07140972847441263</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2190364707154981</v>
+      </c>
+      <c r="C56">
+        <v>2.352705660624817</v>
+      </c>
+      <c r="D56">
+        <v>11.51470566062482</v>
+      </c>
+      <c r="E56">
+        <v>2.521999999999998</v>
+      </c>
+      <c r="F56">
+        <v>18.522</v>
+      </c>
+      <c r="G56">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H56">
+        <v>18.3</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.709</v>
+      </c>
+      <c r="K56">
+        <v>0.399</v>
+      </c>
+      <c r="L56">
+        <v>0.31</v>
+      </c>
+      <c r="M56">
+        <v>4.4230536</v>
+      </c>
+      <c r="N56">
+        <v>-4.113053600000001</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-4.113053600000001</v>
+      </c>
+      <c r="Q56">
+        <v>-3.714053600000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1958358059032568</v>
+      </c>
+      <c r="T56">
+        <v>2.259892674339286</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2388</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.07008732609525681</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2210364707154981</v>
+      </c>
+      <c r="C57">
+        <v>1.883334626161567</v>
+      </c>
+      <c r="D57">
+        <v>11.38833462616156</v>
+      </c>
+      <c r="E57">
+        <v>2.864999999999998</v>
+      </c>
+      <c r="F57">
+        <v>18.865</v>
+      </c>
+      <c r="G57">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H57">
+        <v>18.3</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0.709</v>
+      </c>
+      <c r="K57">
+        <v>0.399</v>
+      </c>
+      <c r="L57">
+        <v>0.31</v>
+      </c>
+      <c r="M57">
+        <v>4.504962</v>
+      </c>
+      <c r="N57">
+        <v>-4.194962</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-4.194962</v>
+      </c>
+      <c r="Q57">
+        <v>-3.795962</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1993254904788847</v>
+      </c>
+      <c r="T57">
+        <v>2.310112511546825</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2388</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.0688130110753431</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2230364707154981</v>
+      </c>
+      <c r="C58">
+        <v>1.416707262025305</v>
+      </c>
+      <c r="D58">
+        <v>11.26470726202531</v>
+      </c>
+      <c r="E58">
+        <v>3.208000000000002</v>
+      </c>
+      <c r="F58">
+        <v>19.208</v>
+      </c>
+      <c r="G58">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H58">
+        <v>18.3</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0.709</v>
+      </c>
+      <c r="K58">
+        <v>0.399</v>
+      </c>
+      <c r="L58">
+        <v>0.31</v>
+      </c>
+      <c r="M58">
+        <v>4.5868704</v>
+      </c>
+      <c r="N58">
+        <v>-4.276870400000001</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-4.276870400000001</v>
+      </c>
+      <c r="Q58">
+        <v>-3.877870400000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2029737970806776</v>
+      </c>
+      <c r="T58">
+        <v>2.362615068627435</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2388</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.06758420730614045</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2250364707154981</v>
+      </c>
+      <c r="C59">
+        <v>0.9527351751000381</v>
+      </c>
+      <c r="D59">
+        <v>11.14373517510004</v>
+      </c>
+      <c r="E59">
+        <v>3.551000000000002</v>
+      </c>
+      <c r="F59">
+        <v>19.551</v>
+      </c>
+      <c r="G59">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H59">
+        <v>18.3</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0.709</v>
+      </c>
+      <c r="K59">
+        <v>0.399</v>
+      </c>
+      <c r="L59">
+        <v>0.31</v>
+      </c>
+      <c r="M59">
+        <v>4.668778800000001</v>
+      </c>
+      <c r="N59">
+        <v>-4.358778800000001</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-4.358778800000001</v>
+      </c>
+      <c r="Q59">
+        <v>-3.959778800000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2067917923616236</v>
+      </c>
+      <c r="T59">
+        <v>2.417559605107143</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2388</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.06639851945866437</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2270364707154981</v>
+      </c>
+      <c r="C60">
+        <v>0.4913337289536912</v>
+      </c>
+      <c r="D60">
+        <v>11.02533372895369</v>
+      </c>
+      <c r="E60">
+        <v>3.893999999999998</v>
+      </c>
+      <c r="F60">
+        <v>19.894</v>
+      </c>
+      <c r="G60">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H60">
+        <v>18.3</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0.709</v>
+      </c>
+      <c r="K60">
+        <v>0.399</v>
+      </c>
+      <c r="L60">
+        <v>0.31</v>
+      </c>
+      <c r="M60">
+        <v>4.7506872</v>
+      </c>
+      <c r="N60">
+        <v>-4.4406872</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-4.4406872</v>
+      </c>
+      <c r="Q60">
+        <v>-4.0416872</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2107915969416621</v>
+      </c>
+      <c r="T60">
+        <v>2.475120548085884</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2388</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.06525371739903219</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2290364707154981</v>
+      </c>
+      <c r="C61">
+        <v>0.03242184636371093</v>
+      </c>
+      <c r="D61">
+        <v>10.90942184636371</v>
+      </c>
+      <c r="E61">
+        <v>4.236999999999998</v>
+      </c>
+      <c r="F61">
+        <v>20.237</v>
+      </c>
+      <c r="G61">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H61">
+        <v>18.3</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0.709</v>
+      </c>
+      <c r="K61">
+        <v>0.399</v>
+      </c>
+      <c r="L61">
+        <v>0.31</v>
+      </c>
+      <c r="M61">
+        <v>4.832595599999999</v>
+      </c>
+      <c r="N61">
+        <v>-4.5225956</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-4.5225956</v>
+      </c>
+      <c r="Q61">
+        <v>-4.1235956</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2149865139402393</v>
+      </c>
+      <c r="T61">
+        <v>2.535489341941637</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2388</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.0641477221888791</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2310364707154981</v>
+      </c>
+      <c r="C62">
+        <v>-0.4240781758304024</v>
+      </c>
+      <c r="D62">
+        <v>10.79592182416959</v>
+      </c>
+      <c r="E62">
+        <v>4.579999999999998</v>
+      </c>
+      <c r="F62">
+        <v>20.58</v>
+      </c>
+      <c r="G62">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H62">
+        <v>18.3</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0.709</v>
+      </c>
+      <c r="K62">
+        <v>0.399</v>
+      </c>
+      <c r="L62">
+        <v>0.31</v>
+      </c>
+      <c r="M62">
+        <v>4.914504</v>
+      </c>
+      <c r="N62">
+        <v>-4.604504</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-4.604504</v>
+      </c>
+      <c r="Q62">
+        <v>-4.205504</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2193911767887453</v>
+      </c>
+      <c r="T62">
+        <v>2.598876575490178</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2388</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.06307859348573108</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2330364707154981</v>
+      </c>
+      <c r="C63">
+        <v>-0.8782408404360886</v>
+      </c>
+      <c r="D63">
+        <v>10.68475915956391</v>
+      </c>
+      <c r="E63">
+        <v>4.922999999999998</v>
+      </c>
+      <c r="F63">
+        <v>20.923</v>
+      </c>
+      <c r="G63">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H63">
+        <v>18.3</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0.709</v>
+      </c>
+      <c r="K63">
+        <v>0.399</v>
+      </c>
+      <c r="L63">
+        <v>0.31</v>
+      </c>
+      <c r="M63">
+        <v>4.9964124</v>
+      </c>
+      <c r="N63">
+        <v>-4.6864124</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-4.6864124</v>
+      </c>
+      <c r="Q63">
+        <v>-4.2874124</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2240217197833285</v>
+      </c>
+      <c r="T63">
+        <v>2.665514436400183</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.06204451818268641</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2350364707154981</v>
+      </c>
+      <c r="C64">
+        <v>-1.330137612994285</v>
+      </c>
+      <c r="D64">
+        <v>10.57586238700571</v>
+      </c>
+      <c r="E64">
+        <v>5.265999999999998</v>
+      </c>
+      <c r="F64">
+        <v>21.266</v>
+      </c>
+      <c r="G64">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H64">
+        <v>18.3</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0.709</v>
+      </c>
+      <c r="K64">
+        <v>0.399</v>
+      </c>
+      <c r="L64">
+        <v>0.31</v>
+      </c>
+      <c r="M64">
+        <v>5.0783208</v>
+      </c>
+      <c r="N64">
+        <v>-4.768320800000001</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-4.768320800000001</v>
+      </c>
+      <c r="Q64">
+        <v>-4.369320800000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2288959755671003</v>
+      </c>
+      <c r="T64">
+        <v>2.735659553147556</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.06104380014748179</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2370364707154981</v>
+      </c>
+      <c r="C65">
+        <v>-1.779837074993726</v>
+      </c>
+      <c r="D65">
+        <v>10.46916292500627</v>
+      </c>
+      <c r="E65">
+        <v>5.608999999999998</v>
+      </c>
+      <c r="F65">
+        <v>21.609</v>
+      </c>
+      <c r="G65">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H65">
+        <v>18.3</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0.709</v>
+      </c>
+      <c r="K65">
+        <v>0.399</v>
+      </c>
+      <c r="L65">
+        <v>0.31</v>
+      </c>
+      <c r="M65">
+        <v>5.1602292</v>
+      </c>
+      <c r="N65">
+        <v>-4.8502292</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-4.8502292</v>
+      </c>
+      <c r="Q65">
+        <v>-4.4512292</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2340337046364814</v>
+      </c>
+      <c r="T65">
+        <v>2.80959629782722</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.06007485093879161</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2390364707154981</v>
+      </c>
+      <c r="C66">
+        <v>-2.227405067903277</v>
+      </c>
+      <c r="D66">
+        <v>10.36459493209672</v>
+      </c>
+      <c r="E66">
+        <v>5.951999999999998</v>
+      </c>
+      <c r="F66">
+        <v>21.952</v>
+      </c>
+      <c r="G66">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H66">
+        <v>18.3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0.709</v>
+      </c>
+      <c r="K66">
+        <v>0.399</v>
+      </c>
+      <c r="L66">
+        <v>0.31</v>
+      </c>
+      <c r="M66">
+        <v>5.2421376</v>
+      </c>
+      <c r="N66">
+        <v>-4.9321376</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-4.9321376</v>
+      </c>
+      <c r="Q66">
+        <v>-4.5331376</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2394568630986058</v>
+      </c>
+      <c r="T66">
+        <v>2.887640639433531</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.05913618139287291</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2410364707154981</v>
+      </c>
+      <c r="C67">
+        <v>-2.672904828657881</v>
+      </c>
+      <c r="D67">
+        <v>10.26209517134212</v>
+      </c>
+      <c r="E67">
+        <v>6.294999999999998</v>
+      </c>
+      <c r="F67">
+        <v>22.295</v>
+      </c>
+      <c r="G67">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H67">
+        <v>18.3</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0.709</v>
+      </c>
+      <c r="K67">
+        <v>0.399</v>
+      </c>
+      <c r="L67">
+        <v>0.31</v>
+      </c>
+      <c r="M67">
+        <v>5.324046</v>
+      </c>
+      <c r="N67">
+        <v>-5.014046</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-5.014046</v>
+      </c>
+      <c r="Q67">
+        <v>-4.615046</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2451899163299946</v>
+      </c>
+      <c r="T67">
+        <v>2.970144657703061</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.05822639398682872</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2430364707154981</v>
+      </c>
+      <c r="C68">
+        <v>-3.116397117183933</v>
+      </c>
+      <c r="D68">
+        <v>10.16160288281607</v>
+      </c>
+      <c r="E68">
+        <v>6.637999999999998</v>
+      </c>
+      <c r="F68">
+        <v>22.638</v>
+      </c>
+      <c r="G68">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H68">
+        <v>18.3</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0.709</v>
+      </c>
+      <c r="K68">
+        <v>0.399</v>
+      </c>
+      <c r="L68">
+        <v>0.31</v>
+      </c>
+      <c r="M68">
+        <v>5.4059544</v>
+      </c>
+      <c r="N68">
+        <v>-5.0959544</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-5.0959544</v>
+      </c>
+      <c r="Q68">
+        <v>-4.6969544</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2512602079867592</v>
+      </c>
+      <c r="T68">
+        <v>3.057501853517857</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.05734417589611918</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2450364707154981</v>
+      </c>
+      <c r="C69">
+        <v>-3.557940336504576</v>
+      </c>
+      <c r="D69">
+        <v>10.06305966349542</v>
+      </c>
+      <c r="E69">
+        <v>6.980999999999998</v>
+      </c>
+      <c r="F69">
+        <v>22.981</v>
+      </c>
+      <c r="G69">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H69">
+        <v>18.3</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0.709</v>
+      </c>
+      <c r="K69">
+        <v>0.399</v>
+      </c>
+      <c r="L69">
+        <v>0.31</v>
+      </c>
+      <c r="M69">
+        <v>5.4878628</v>
+      </c>
+      <c r="N69">
+        <v>-5.177862800000001</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-5.177862800000001</v>
+      </c>
+      <c r="Q69">
+        <v>-4.778862800000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2576983961075701</v>
+      </c>
+      <c r="T69">
+        <v>3.15015342483658</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.05648829267378908</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2470364707154981</v>
+      </c>
+      <c r="C70">
+        <v>-3.997590645923658</v>
+      </c>
+      <c r="D70">
+        <v>9.966409354076342</v>
+      </c>
+      <c r="E70">
+        <v>7.323999999999998</v>
+      </c>
+      <c r="F70">
+        <v>23.324</v>
+      </c>
+      <c r="G70">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H70">
+        <v>18.3</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0.709</v>
+      </c>
+      <c r="K70">
+        <v>0.399</v>
+      </c>
+      <c r="L70">
+        <v>0.31</v>
+      </c>
+      <c r="M70">
+        <v>5.5697712</v>
+      </c>
+      <c r="N70">
+        <v>-5.2597712</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-5.2597712</v>
+      </c>
+      <c r="Q70">
+        <v>-4.8607712</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2645389709859316</v>
+      </c>
+      <c r="T70">
+        <v>3.248595719362723</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.05565758248740982</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2490364707154981</v>
+      </c>
+      <c r="C71">
+        <v>-4.435402067749358</v>
+      </c>
+      <c r="D71">
+        <v>9.871597932250644</v>
+      </c>
+      <c r="E71">
+        <v>7.667000000000002</v>
+      </c>
+      <c r="F71">
+        <v>23.667</v>
+      </c>
+      <c r="G71">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H71">
+        <v>18.3</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0.709</v>
+      </c>
+      <c r="K71">
+        <v>0.399</v>
+      </c>
+      <c r="L71">
+        <v>0.31</v>
+      </c>
+      <c r="M71">
+        <v>5.6516796</v>
+      </c>
+      <c r="N71">
+        <v>-5.341679600000001</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-5.341679600000001</v>
+      </c>
+      <c r="Q71">
+        <v>-4.942679600000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2718208732758004</v>
+      </c>
+      <c r="T71">
+        <v>3.353389129664747</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.05485095085715752</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2510364707154981</v>
+      </c>
+      <c r="C72">
+        <v>-4.871426587983517</v>
+      </c>
+      <c r="D72">
+        <v>9.778573412016485</v>
+      </c>
+      <c r="E72">
+        <v>8.010000000000002</v>
+      </c>
+      <c r="F72">
+        <v>24.01</v>
+      </c>
+      <c r="G72">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H72">
+        <v>18.3</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0.709</v>
+      </c>
+      <c r="K72">
+        <v>0.399</v>
+      </c>
+      <c r="L72">
+        <v>0.31</v>
+      </c>
+      <c r="M72">
+        <v>5.733588000000001</v>
+      </c>
+      <c r="N72">
+        <v>-5.423588000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-5.423588000000001</v>
+      </c>
+      <c r="Q72">
+        <v>-5.024588000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.279588235718327</v>
+      </c>
+      <c r="T72">
+        <v>3.465168767320238</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.05406736584491234</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2530364707154981</v>
+      </c>
+      <c r="C73">
+        <v>-5.305714251371157</v>
+      </c>
+      <c r="D73">
+        <v>9.687285748628842</v>
+      </c>
+      <c r="E73">
+        <v>8.352999999999998</v>
+      </c>
+      <c r="F73">
+        <v>24.353</v>
+      </c>
+      <c r="G73">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H73">
+        <v>18.3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0.709</v>
+      </c>
+      <c r="K73">
+        <v>0.399</v>
+      </c>
+      <c r="L73">
+        <v>0.31</v>
+      </c>
+      <c r="M73">
+        <v>5.8154964</v>
+      </c>
+      <c r="N73">
+        <v>-5.5054964</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-5.5054964</v>
+      </c>
+      <c r="Q73">
+        <v>-5.1064964</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2878912783293038</v>
+      </c>
+      <c r="T73">
+        <v>3.584657345503694</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.05330585364991369</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2550364707154981</v>
+      </c>
+      <c r="C74">
+        <v>-5.738313251175168</v>
+      </c>
+      <c r="D74">
+        <v>9.597686748824831</v>
+      </c>
+      <c r="E74">
+        <v>8.695999999999998</v>
+      </c>
+      <c r="F74">
+        <v>24.696</v>
+      </c>
+      <c r="G74">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H74">
+        <v>18.3</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0.709</v>
+      </c>
+      <c r="K74">
+        <v>0.399</v>
+      </c>
+      <c r="L74">
+        <v>0.31</v>
+      </c>
+      <c r="M74">
+        <v>5.897404799999999</v>
+      </c>
+      <c r="N74">
+        <v>-5.5874048</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-5.5874048</v>
+      </c>
+      <c r="Q74">
+        <v>-5.1884048</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2967873954124932</v>
+      </c>
+      <c r="T74">
+        <v>3.712680822128826</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.05256549457144266</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2570364707154981</v>
+      </c>
+      <c r="C75">
+        <v>-6.169270014014653</v>
+      </c>
+      <c r="D75">
+        <v>9.509729985985345</v>
+      </c>
+      <c r="E75">
+        <v>9.038999999999998</v>
+      </c>
+      <c r="F75">
+        <v>25.039</v>
+      </c>
+      <c r="G75">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H75">
+        <v>18.3</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0.709</v>
+      </c>
+      <c r="K75">
+        <v>0.399</v>
+      </c>
+      <c r="L75">
+        <v>0.31</v>
+      </c>
+      <c r="M75">
+        <v>5.9793132</v>
+      </c>
+      <c r="N75">
+        <v>-5.6693132</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-5.6693132</v>
+      </c>
+      <c r="Q75">
+        <v>-5.2703132</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3063424841314745</v>
+      </c>
+      <c r="T75">
+        <v>3.850187519244708</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.05184541930334063</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2590364707154981</v>
+      </c>
+      <c r="C76">
+        <v>-6.598629280080715</v>
+      </c>
+      <c r="D76">
+        <v>9.423370719919282</v>
+      </c>
+      <c r="E76">
+        <v>9.381999999999998</v>
+      </c>
+      <c r="F76">
+        <v>25.382</v>
+      </c>
+      <c r="G76">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H76">
+        <v>18.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0.709</v>
+      </c>
+      <c r="K76">
+        <v>0.399</v>
+      </c>
+      <c r="L76">
+        <v>0.31</v>
+      </c>
+      <c r="M76">
+        <v>6.0612216</v>
+      </c>
+      <c r="N76">
+        <v>-5.7512216</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-5.7512216</v>
+      </c>
+      <c r="Q76">
+        <v>-5.3522216</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3166325796749927</v>
+      </c>
+      <c r="T76">
+        <v>3.998271654600274</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.05114480552897116</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2610364707154981</v>
+      </c>
+      <c r="C77">
+        <v>-7.026434179020846</v>
+      </c>
+      <c r="D77">
+        <v>9.338565820979152</v>
+      </c>
+      <c r="E77">
+        <v>9.724999999999998</v>
+      </c>
+      <c r="F77">
+        <v>25.725</v>
+      </c>
+      <c r="G77">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H77">
+        <v>18.3</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0.709</v>
+      </c>
+      <c r="K77">
+        <v>0.399</v>
+      </c>
+      <c r="L77">
+        <v>0.31</v>
+      </c>
+      <c r="M77">
+        <v>6.14313</v>
+      </c>
+      <c r="N77">
+        <v>-5.833130000000001</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-5.833130000000001</v>
+      </c>
+      <c r="Q77">
+        <v>-5.434130000000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3277458828619924</v>
+      </c>
+      <c r="T77">
+        <v>4.158202520784285</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.05046287478858491</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2630364707154981</v>
+      </c>
+      <c r="C78">
+        <v>-7.452726301762354</v>
+      </c>
+      <c r="D78">
+        <v>9.255273698237643</v>
+      </c>
+      <c r="E78">
+        <v>10.068</v>
+      </c>
+      <c r="F78">
+        <v>26.068</v>
+      </c>
+      <c r="G78">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H78">
+        <v>18.3</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0.709</v>
+      </c>
+      <c r="K78">
+        <v>0.399</v>
+      </c>
+      <c r="L78">
+        <v>0.31</v>
+      </c>
+      <c r="M78">
+        <v>6.2250384</v>
+      </c>
+      <c r="N78">
+        <v>-5.9150384</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-5.9150384</v>
+      </c>
+      <c r="Q78">
+        <v>-5.5160384</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3397852946479089</v>
+      </c>
+      <c r="T78">
+        <v>4.331460959150298</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.04979888959399825</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2650364707154981</v>
+      </c>
+      <c r="C79">
+        <v>-7.8775457685262</v>
+      </c>
+      <c r="D79">
+        <v>9.1734542314738</v>
+      </c>
+      <c r="E79">
+        <v>10.411</v>
+      </c>
+      <c r="F79">
+        <v>26.411</v>
+      </c>
+      <c r="G79">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H79">
+        <v>18.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.709</v>
+      </c>
+      <c r="K79">
+        <v>0.399</v>
+      </c>
+      <c r="L79">
+        <v>0.31</v>
+      </c>
+      <c r="M79">
+        <v>6.3069468</v>
+      </c>
+      <c r="N79">
+        <v>-5.9969468</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-5.9969468</v>
+      </c>
+      <c r="Q79">
+        <v>-5.5979468</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3528716118065136</v>
+      </c>
+      <c r="T79">
+        <v>4.519785348678571</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.0491521507681022</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2670364707154981</v>
+      </c>
+      <c r="C80">
+        <v>-8.300931293264782</v>
+      </c>
+      <c r="D80">
+        <v>9.093068706735218</v>
+      </c>
+      <c r="E80">
+        <v>10.754</v>
+      </c>
+      <c r="F80">
+        <v>26.754</v>
+      </c>
+      <c r="G80">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H80">
+        <v>18.3</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0.709</v>
+      </c>
+      <c r="K80">
+        <v>0.399</v>
+      </c>
+      <c r="L80">
+        <v>0.31</v>
+      </c>
+      <c r="M80">
+        <v>6.3888552</v>
+      </c>
+      <c r="N80">
+        <v>-6.0788552</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-6.0788552</v>
+      </c>
+      <c r="Q80">
+        <v>-5.6798552</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3671475941613551</v>
+      </c>
+      <c r="T80">
+        <v>4.72523013725487</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.04852199498902399</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2690364707154981</v>
+      </c>
+      <c r="C81">
+        <v>-8.722920244741296</v>
+      </c>
+      <c r="D81">
+        <v>9.014079755258702</v>
+      </c>
+      <c r="E81">
+        <v>11.097</v>
+      </c>
+      <c r="F81">
+        <v>27.097</v>
+      </c>
+      <c r="G81">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H81">
+        <v>18.3</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0.709</v>
+      </c>
+      <c r="K81">
+        <v>0.399</v>
+      </c>
+      <c r="L81">
+        <v>0.31</v>
+      </c>
+      <c r="M81">
+        <v>6.4707636</v>
+      </c>
+      <c r="N81">
+        <v>-6.1607636</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-6.1607636</v>
+      </c>
+      <c r="Q81">
+        <v>-5.7617636</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3827831938833244</v>
+      </c>
+      <c r="T81">
+        <v>4.950241096171769</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.04790779252080846</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2710364707154981</v>
+      </c>
+      <c r="C82">
+        <v>-9.143548704452961</v>
+      </c>
+      <c r="D82">
+        <v>8.936451295547037</v>
+      </c>
+      <c r="E82">
+        <v>11.44</v>
+      </c>
+      <c r="F82">
+        <v>27.44</v>
+      </c>
+      <c r="G82">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H82">
+        <v>18.3</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0.709</v>
+      </c>
+      <c r="K82">
+        <v>0.399</v>
+      </c>
+      <c r="L82">
+        <v>0.31</v>
+      </c>
+      <c r="M82">
+        <v>6.552671999999999</v>
+      </c>
+      <c r="N82">
+        <v>-6.242672</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-6.242672</v>
+      </c>
+      <c r="Q82">
+        <v>-5.843672</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3999823535774906</v>
+      </c>
+      <c r="T82">
+        <v>5.197753150980358</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.0473089451142984</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2730364707154981</v>
+      </c>
+      <c r="C83">
+        <v>-9.562851521586861</v>
+      </c>
+      <c r="D83">
+        <v>8.860148478413141</v>
+      </c>
+      <c r="E83">
+        <v>11.783</v>
+      </c>
+      <c r="F83">
+        <v>27.783</v>
+      </c>
+      <c r="G83">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H83">
+        <v>18.3</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0.709</v>
+      </c>
+      <c r="K83">
+        <v>0.399</v>
+      </c>
+      <c r="L83">
+        <v>0.31</v>
+      </c>
+      <c r="M83">
+        <v>6.634580400000001</v>
+      </c>
+      <c r="N83">
+        <v>-6.324580400000001</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-6.324580400000001</v>
+      </c>
+      <c r="Q83">
+        <v>-5.925580400000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4189919511342007</v>
+      </c>
+      <c r="T83">
+        <v>5.471319106295113</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.0467248840635045</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2750364707154981</v>
+      </c>
+      <c r="C84">
+        <v>-9.980862365184191</v>
+      </c>
+      <c r="D84">
+        <v>8.785137634815809</v>
+      </c>
+      <c r="E84">
+        <v>12.126</v>
+      </c>
+      <c r="F84">
+        <v>28.126</v>
+      </c>
+      <c r="G84">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H84">
+        <v>18.3</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0.709</v>
+      </c>
+      <c r="K84">
+        <v>0.399</v>
+      </c>
+      <c r="L84">
+        <v>0.31</v>
+      </c>
+      <c r="M84">
+        <v>6.7164888</v>
+      </c>
+      <c r="N84">
+        <v>-6.406488800000001</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-6.406488800000001</v>
+      </c>
+      <c r="Q84">
+        <v>-6.007488800000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4401137261972118</v>
+      </c>
+      <c r="T84">
+        <v>5.775281278867064</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.04615506840419348</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2770364707154981</v>
+      </c>
+      <c r="C85">
+        <v>-10.39761377367704</v>
+      </c>
+      <c r="D85">
+        <v>8.711386226322965</v>
+      </c>
+      <c r="E85">
+        <v>12.469</v>
+      </c>
+      <c r="F85">
+        <v>28.469</v>
+      </c>
+      <c r="G85">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H85">
+        <v>18.3</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0.709</v>
+      </c>
+      <c r="K85">
+        <v>0.399</v>
+      </c>
+      <c r="L85">
+        <v>0.31</v>
+      </c>
+      <c r="M85">
+        <v>6.798397200000001</v>
+      </c>
+      <c r="N85">
+        <v>-6.488397200000001</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-6.488397200000001</v>
+      </c>
+      <c r="Q85">
+        <v>-6.089397200000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4637204159735184</v>
+      </c>
+      <c r="T85">
+        <v>6.115003707035716</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.04559898324269718</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2790364707154981</v>
+      </c>
+      <c r="C86">
+        <v>-10.81313720195066</v>
+      </c>
+      <c r="D86">
+        <v>8.638862798049336</v>
+      </c>
+      <c r="E86">
+        <v>12.812</v>
+      </c>
+      <c r="F86">
+        <v>28.812</v>
+      </c>
+      <c r="G86">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H86">
+        <v>18.3</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0.709</v>
+      </c>
+      <c r="K86">
+        <v>0.399</v>
+      </c>
+      <c r="L86">
+        <v>0.31</v>
+      </c>
+      <c r="M86">
+        <v>6.8803056</v>
+      </c>
+      <c r="N86">
+        <v>-6.5703056</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-6.5703056</v>
+      </c>
+      <c r="Q86">
+        <v>-6.1713056</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4902779419718631</v>
+      </c>
+      <c r="T86">
+        <v>6.497191438725444</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.04505613820409371</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2810364707154981</v>
+      </c>
+      <c r="C87">
+        <v>-11.22746306607453</v>
+      </c>
+      <c r="D87">
+        <v>8.567536933925469</v>
+      </c>
+      <c r="E87">
+        <v>13.155</v>
+      </c>
+      <c r="F87">
+        <v>29.155</v>
+      </c>
+      <c r="G87">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H87">
+        <v>18.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0.709</v>
+      </c>
+      <c r="K87">
+        <v>0.399</v>
+      </c>
+      <c r="L87">
+        <v>0.31</v>
+      </c>
+      <c r="M87">
+        <v>6.962213999999999</v>
+      </c>
+      <c r="N87">
+        <v>-6.652214</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-6.652214</v>
+      </c>
+      <c r="Q87">
+        <v>-6.253214</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.520376471436654</v>
+      </c>
+      <c r="T87">
+        <v>6.930337534640475</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.04452606598992781</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2830364707154981</v>
+      </c>
+      <c r="C88">
+        <v>-11.64062078583544</v>
+      </c>
+      <c r="D88">
+        <v>8.497379214164562</v>
+      </c>
+      <c r="E88">
+        <v>13.498</v>
+      </c>
+      <c r="F88">
+        <v>29.498</v>
+      </c>
+      <c r="G88">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H88">
+        <v>18.3</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0.709</v>
+      </c>
+      <c r="K88">
+        <v>0.399</v>
+      </c>
+      <c r="L88">
+        <v>0.31</v>
+      </c>
+      <c r="M88">
+        <v>7.0441224</v>
+      </c>
+      <c r="N88">
+        <v>-6.7341224</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-6.7341224</v>
+      </c>
+      <c r="Q88">
+        <v>-6.3351224</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5547747908249865</v>
+      </c>
+      <c r="T88">
+        <v>7.425361644257651</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.04400832103655661</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2850364707154981</v>
+      </c>
+      <c r="C89">
+        <v>-12.05263882519795</v>
+      </c>
+      <c r="D89">
+        <v>8.428361174802045</v>
+      </c>
+      <c r="E89">
+        <v>13.841</v>
+      </c>
+      <c r="F89">
+        <v>29.841</v>
+      </c>
+      <c r="G89">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H89">
+        <v>18.3</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0.709</v>
+      </c>
+      <c r="K89">
+        <v>0.399</v>
+      </c>
+      <c r="L89">
+        <v>0.31</v>
+      </c>
+      <c r="M89">
+        <v>7.1260308</v>
+      </c>
+      <c r="N89">
+        <v>-6.8160308</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-6.8160308</v>
+      </c>
+      <c r="Q89">
+        <v>-6.4170308</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5944651593499855</v>
+      </c>
+      <c r="T89">
+        <v>7.996543309200548</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.04350247826602149</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2870364707154981</v>
+      </c>
+      <c r="C90">
+        <v>-12.46354473080891</v>
+      </c>
+      <c r="D90">
+        <v>8.360455269191084</v>
+      </c>
+      <c r="E90">
+        <v>14.184</v>
+      </c>
+      <c r="F90">
+        <v>30.184</v>
+      </c>
+      <c r="G90">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H90">
+        <v>18.3</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0.709</v>
+      </c>
+      <c r="K90">
+        <v>0.399</v>
+      </c>
+      <c r="L90">
+        <v>0.31</v>
+      </c>
+      <c r="M90">
+        <v>7.2079392</v>
+      </c>
+      <c r="N90">
+        <v>-6.897939200000001</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-6.897939200000001</v>
+      </c>
+      <c r="Q90">
+        <v>-6.498939200000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6407705892958178</v>
+      </c>
+      <c r="T90">
+        <v>8.662921918300595</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.04300813192208941</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2890364707154982</v>
+      </c>
+      <c r="C91">
+        <v>-12.87336516865545</v>
+      </c>
+      <c r="D91">
+        <v>8.293634831344546</v>
+      </c>
+      <c r="E91">
+        <v>14.527</v>
+      </c>
+      <c r="F91">
+        <v>30.527</v>
+      </c>
+      <c r="G91">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H91">
+        <v>18.3</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0.709</v>
+      </c>
+      <c r="K91">
+        <v>0.399</v>
+      </c>
+      <c r="L91">
+        <v>0.31</v>
+      </c>
+      <c r="M91">
+        <v>7.2898476</v>
+      </c>
+      <c r="N91">
+        <v>-6.9798476</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-6.9798476</v>
+      </c>
+      <c r="Q91">
+        <v>-6.5808476</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6954951883227103</v>
+      </c>
+      <c r="T91">
+        <v>9.450460274509741</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.0425248944847626</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2910364707154981</v>
+      </c>
+      <c r="C92">
+        <v>-13.28212595897906</v>
+      </c>
+      <c r="D92">
+        <v>8.227874041020939</v>
+      </c>
+      <c r="E92">
+        <v>14.87</v>
+      </c>
+      <c r="F92">
+        <v>30.87</v>
+      </c>
+      <c r="G92">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H92">
+        <v>18.3</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0.709</v>
+      </c>
+      <c r="K92">
+        <v>0.399</v>
+      </c>
+      <c r="L92">
+        <v>0.31</v>
+      </c>
+      <c r="M92">
+        <v>7.371756</v>
+      </c>
+      <c r="N92">
+        <v>-7.061756</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-7.061756</v>
+      </c>
+      <c r="Q92">
+        <v>-6.662756</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7611647071549812</v>
+      </c>
+      <c r="T92">
+        <v>10.39550630196072</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.04205239565715413</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2930364707154981</v>
+      </c>
+      <c r="C93">
+        <v>-13.68985210954169</v>
+      </c>
+      <c r="D93">
+        <v>8.163147890458312</v>
+      </c>
+      <c r="E93">
+        <v>15.213</v>
+      </c>
+      <c r="F93">
+        <v>31.213</v>
+      </c>
+      <c r="G93">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H93">
+        <v>18.3</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0.709</v>
+      </c>
+      <c r="K93">
+        <v>0.399</v>
+      </c>
+      <c r="L93">
+        <v>0.31</v>
+      </c>
+      <c r="M93">
+        <v>7.4536644</v>
+      </c>
+      <c r="N93">
+        <v>-7.1436644</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-7.1436644</v>
+      </c>
+      <c r="Q93">
+        <v>-6.7446644</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8414274523944236</v>
+      </c>
+      <c r="T93">
+        <v>11.55056255773413</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.04159028141916343</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2950364707154982</v>
+      </c>
+      <c r="C94">
+        <v>-14.09656784733392</v>
+      </c>
+      <c r="D94">
+        <v>8.099432152666074</v>
+      </c>
+      <c r="E94">
+        <v>15.556</v>
+      </c>
+      <c r="F94">
+        <v>31.556</v>
+      </c>
+      <c r="G94">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H94">
+        <v>18.3</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0.709</v>
+      </c>
+      <c r="K94">
+        <v>0.399</v>
+      </c>
+      <c r="L94">
+        <v>0.31</v>
+      </c>
+      <c r="M94">
+        <v>7.5355728</v>
+      </c>
+      <c r="N94">
+        <v>-7.2255728</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-7.2255728</v>
+      </c>
+      <c r="Q94">
+        <v>-6.8265728</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.941755883943727</v>
+      </c>
+      <c r="T94">
+        <v>12.9943828774509</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.04113821314286814</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2970364707154982</v>
+      </c>
+      <c r="C95">
+        <v>-14.50229664880976</v>
+      </c>
+      <c r="D95">
+        <v>8.036703351190241</v>
+      </c>
+      <c r="E95">
+        <v>15.899</v>
+      </c>
+      <c r="F95">
+        <v>31.899</v>
+      </c>
+      <c r="G95">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H95">
+        <v>18.3</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0.709</v>
+      </c>
+      <c r="K95">
+        <v>0.399</v>
+      </c>
+      <c r="L95">
+        <v>0.31</v>
+      </c>
+      <c r="M95">
+        <v>7.617481199999999</v>
+      </c>
+      <c r="N95">
+        <v>-7.3074812</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-7.3074812</v>
+      </c>
+      <c r="Q95">
+        <v>-6.9084812</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.070749581649974</v>
+      </c>
+      <c r="T95">
+        <v>14.85072328851532</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.04069586676498782</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2990364707154981</v>
+      </c>
+      <c r="C96">
+        <v>-14.90706126872712</v>
+      </c>
+      <c r="D96">
+        <v>7.974938731272875</v>
+      </c>
+      <c r="E96">
+        <v>16.242</v>
+      </c>
+      <c r="F96">
+        <v>32.242</v>
+      </c>
+      <c r="G96">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H96">
+        <v>18.3</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0.709</v>
+      </c>
+      <c r="K96">
+        <v>0.399</v>
+      </c>
+      <c r="L96">
+        <v>0.31</v>
+      </c>
+      <c r="M96">
+        <v>7.6993896</v>
+      </c>
+      <c r="N96">
+        <v>-7.3893896</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-7.3893896</v>
+      </c>
+      <c r="Q96">
+        <v>-6.9903896</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.242741178591636</v>
+      </c>
+      <c r="T96">
+        <v>17.32584383660121</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0402629320121688</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3010364707154982</v>
+      </c>
+      <c r="C97">
+        <v>-15.31088376766874</v>
+      </c>
+      <c r="D97">
+        <v>7.914116232331258</v>
+      </c>
+      <c r="E97">
+        <v>16.585</v>
+      </c>
+      <c r="F97">
+        <v>32.585</v>
+      </c>
+      <c r="G97">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H97">
+        <v>18.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0.709</v>
+      </c>
+      <c r="K97">
+        <v>0.399</v>
+      </c>
+      <c r="L97">
+        <v>0.31</v>
+      </c>
+      <c r="M97">
+        <v>7.781298</v>
+      </c>
+      <c r="N97">
+        <v>-7.471298000000001</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-7.471298000000001</v>
+      </c>
+      <c r="Q97">
+        <v>-7.072298000000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.483529414309964</v>
+      </c>
+      <c r="T97">
+        <v>20.79101260392146</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.0398391116751986</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3030364707154981</v>
+      </c>
+      <c r="C98">
+        <v>-15.71378553831305</v>
+      </c>
+      <c r="D98">
+        <v>7.854214461686947</v>
+      </c>
+      <c r="E98">
+        <v>16.928</v>
+      </c>
+      <c r="F98">
+        <v>32.928</v>
+      </c>
+      <c r="G98">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H98">
+        <v>18.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0.709</v>
+      </c>
+      <c r="K98">
+        <v>0.399</v>
+      </c>
+      <c r="L98">
+        <v>0.31</v>
+      </c>
+      <c r="M98">
+        <v>7.8632064</v>
+      </c>
+      <c r="N98">
+        <v>-7.553206400000001</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-7.553206400000001</v>
+      </c>
+      <c r="Q98">
+        <v>-7.154206400000001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.844711767887451</v>
+      </c>
+      <c r="T98">
+        <v>25.98876575490176</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.03942412092858194</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3050364707154981</v>
+      </c>
+      <c r="C99">
+        <v>-16.11578733052115</v>
+      </c>
+      <c r="D99">
+        <v>7.795212669478848</v>
+      </c>
+      <c r="E99">
+        <v>17.27099999999999</v>
+      </c>
+      <c r="F99">
+        <v>33.27099999999999</v>
+      </c>
+      <c r="G99">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H99">
+        <v>18.3</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0.709</v>
+      </c>
+      <c r="K99">
+        <v>0.399</v>
+      </c>
+      <c r="L99">
+        <v>0.31</v>
+      </c>
+      <c r="M99">
+        <v>7.945114799999999</v>
+      </c>
+      <c r="N99">
+        <v>-7.635114799999999</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-7.635114799999999</v>
+      </c>
+      <c r="Q99">
+        <v>-7.236114799999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.446682357183268</v>
+      </c>
+      <c r="T99">
+        <v>34.65168767320235</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.03901768669220484</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3070364707154981</v>
+      </c>
+      <c r="C100">
+        <v>-16.51690927530133</v>
+      </c>
+      <c r="D100">
+        <v>7.737090724698663</v>
+      </c>
+      <c r="E100">
+        <v>17.614</v>
+      </c>
+      <c r="F100">
+        <v>33.614</v>
+      </c>
+      <c r="G100">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H100">
+        <v>18.3</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0.709</v>
+      </c>
+      <c r="K100">
+        <v>0.399</v>
+      </c>
+      <c r="L100">
+        <v>0.31</v>
+      </c>
+      <c r="M100">
+        <v>8.0270232</v>
+      </c>
+      <c r="N100">
+        <v>-7.717023200000001</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-7.717023200000001</v>
+      </c>
+      <c r="Q100">
+        <v>-7.318023200000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.650623535774902</v>
+      </c>
+      <c r="T100">
+        <v>51.97753150980352</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.03861954703208026</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3090364707154981</v>
+      </c>
+      <c r="C101">
+        <v>-16.91717090770952</v>
+      </c>
+      <c r="D101">
+        <v>7.679829092290474</v>
+      </c>
+      <c r="E101">
+        <v>17.95699999999999</v>
+      </c>
+      <c r="F101">
+        <v>33.95699999999999</v>
+      </c>
+      <c r="G101">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H101">
+        <v>18.3</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0.709</v>
+      </c>
+      <c r="K101">
+        <v>0.399</v>
+      </c>
+      <c r="L101">
+        <v>0.31</v>
+      </c>
+      <c r="M101">
+        <v>8.108931599999998</v>
+      </c>
+      <c r="N101">
+        <v>-7.798931599999999</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-7.798931599999999</v>
+      </c>
+      <c r="Q101">
+        <v>-7.399931599999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.262447071549804</v>
+      </c>
+      <c r="T101">
+        <v>103.955063019607</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.03822945059741278</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
